--- a/tiflow-xborder/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERPEU-PR-PAR-EU-GET-Prescription-Input.xlsx
+++ b/tiflow-xborder/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERPEU-PR-PAR-EU-GET-Prescription-Input.xlsx
@@ -608,7 +608,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://gematik.de/fhir/erp-eu/ValueSet/GEM_ERPEU_VS_RequestType</t>
+    <t>https://gematik.de/fhir/tiflow-xborder/ValueSet/GEM-ERPEU-VS-RequestType</t>
   </si>
   <si>
     <t>Parameters.parameter:requestData.part:requesttype.value[x].id</t>
